--- a/artfynd/A 29807-2021 artfynd.xlsx
+++ b/artfynd/A 29807-2021 artfynd.xlsx
@@ -2938,10 +2938,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112387446</v>
+        <v>112778326</v>
       </c>
       <c r="B22" t="n">
-        <v>91290</v>
+        <v>91282</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2950,25 +2950,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2981,13 +2981,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>801284</v>
+        <v>801667</v>
       </c>
       <c r="R22" t="n">
-        <v>7225974</v>
+        <v>7225861</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112778326</v>
+        <v>112387446</v>
       </c>
       <c r="B23" t="n">
-        <v>91282</v>
+        <v>91290</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3066,25 +3066,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3097,13 +3097,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>801667</v>
+        <v>801284</v>
       </c>
       <c r="R23" t="n">
-        <v>7225861</v>
+        <v>7225974</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111959803</v>
+        <v>112779893</v>
       </c>
       <c r="B33" t="n">
-        <v>91276</v>
+        <v>91290</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4220,42 +4220,44 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Degernäsmyren, Vb</t>
+          <t>degernäsgrundet, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>801306</v>
+        <v>801160</v>
       </c>
       <c r="R33" t="n">
-        <v>7226050</v>
+        <v>7225992</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4284,7 +4286,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4294,7 +4296,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4303,6 +4305,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4321,7 +4324,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112778481</v>
+        <v>111959803</v>
       </c>
       <c r="B34" t="n">
         <v>91276</v>
@@ -4355,22 +4358,20 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>degernäsgrundet, Vb</t>
+          <t>Degernäsmyren, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>801343</v>
+        <v>801306</v>
       </c>
       <c r="R34" t="n">
-        <v>7225967</v>
+        <v>7226050</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4399,7 +4400,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4409,7 +4410,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4418,7 +4419,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112778368</v>
+        <v>112778481</v>
       </c>
       <c r="B35" t="n">
-        <v>90924</v>
+        <v>91276</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4453,21 +4453,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4745</v>
+        <v>3100</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>801302</v>
+        <v>801343</v>
       </c>
       <c r="R35" t="n">
-        <v>7226025</v>
+        <v>7225967</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112778526</v>
+        <v>112778368</v>
       </c>
       <c r="B36" t="n">
-        <v>91302</v>
+        <v>90924</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4565,25 +4565,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4366</v>
+        <v>4745</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>801294</v>
+        <v>801302</v>
       </c>
       <c r="R36" t="n">
-        <v>7226013</v>
+        <v>7226025</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112779893</v>
+        <v>112778526</v>
       </c>
       <c r="B37" t="n">
-        <v>91290</v>
+        <v>91302</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4685,21 +4685,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>801160</v>
+        <v>801294</v>
       </c>
       <c r="R37" t="n">
-        <v>7225992</v>
+        <v>7226013</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>

--- a/artfynd/A 29807-2021 artfynd.xlsx
+++ b/artfynd/A 29807-2021 artfynd.xlsx
@@ -2245,7 +2245,7 @@
         <v>112387439</v>
       </c>
       <c r="B16" t="n">
-        <v>91290</v>
+        <v>91306</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2358,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112778533</v>
+        <v>112779921</v>
       </c>
       <c r="B17" t="n">
-        <v>91290</v>
+        <v>91306</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801302</v>
+        <v>801657</v>
       </c>
       <c r="R17" t="n">
-        <v>7225991</v>
+        <v>7225926</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2474,10 +2474,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112778442</v>
+        <v>111959803</v>
       </c>
       <c r="B18" t="n">
-        <v>90049</v>
+        <v>91292</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2490,40 +2490,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>3100</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>degernäsgrundet, Vb</t>
+          <t>Degernäsmyren, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801472</v>
+        <v>801306</v>
       </c>
       <c r="R18" t="n">
-        <v>7225939</v>
+        <v>7226050</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2552,7 +2550,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2560,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,7 +2569,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2590,10 +2587,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112780261</v>
+        <v>112778397</v>
       </c>
       <c r="B19" t="n">
-        <v>91290</v>
+        <v>91292</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2602,25 +2599,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2633,13 +2630,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801272</v>
+        <v>801307</v>
       </c>
       <c r="R19" t="n">
-        <v>7226055</v>
+        <v>7226037</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2706,10 +2703,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112780264</v>
+        <v>112778466</v>
       </c>
       <c r="B20" t="n">
-        <v>91290</v>
+        <v>91292</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,25 +2715,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2749,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>801228</v>
+        <v>801318</v>
       </c>
       <c r="R20" t="n">
-        <v>7226025</v>
+        <v>7226056</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2822,10 +2819,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112778412</v>
+        <v>112778481</v>
       </c>
       <c r="B21" t="n">
-        <v>91333</v>
+        <v>91292</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2838,21 +2835,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5448</v>
+        <v>3100</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2865,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>801332</v>
+        <v>801343</v>
       </c>
       <c r="R21" t="n">
-        <v>7225981</v>
+        <v>7225967</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2938,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112778326</v>
+        <v>112779902</v>
       </c>
       <c r="B22" t="n">
-        <v>91282</v>
+        <v>91318</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2950,25 +2947,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2981,10 +2978,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>801667</v>
+        <v>801318</v>
       </c>
       <c r="R22" t="n">
-        <v>7225861</v>
+        <v>7225959</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3054,10 +3051,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112387446</v>
+        <v>112779914</v>
       </c>
       <c r="B23" t="n">
-        <v>91290</v>
+        <v>91306</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3097,13 +3094,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>801284</v>
+        <v>801630</v>
       </c>
       <c r="R23" t="n">
-        <v>7225974</v>
+        <v>7225910</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3170,10 +3167,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112778397</v>
+        <v>112778391</v>
       </c>
       <c r="B24" t="n">
-        <v>91276</v>
+        <v>91349</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3186,21 +3183,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3100</v>
+        <v>5448</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3213,13 +3210,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>801307</v>
+        <v>801314</v>
       </c>
       <c r="R24" t="n">
-        <v>7226037</v>
+        <v>7226071</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3286,10 +3283,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112779902</v>
+        <v>112778526</v>
       </c>
       <c r="B25" t="n">
-        <v>91302</v>
+        <v>91318</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3329,10 +3326,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>801318</v>
+        <v>801294</v>
       </c>
       <c r="R25" t="n">
-        <v>7225959</v>
+        <v>7226013</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3402,10 +3399,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112778350</v>
+        <v>112778514</v>
       </c>
       <c r="B26" t="n">
-        <v>90047</v>
+        <v>91306</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3414,25 +3411,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3445,10 +3442,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>801521</v>
+        <v>801257</v>
       </c>
       <c r="R26" t="n">
-        <v>7225910</v>
+        <v>7226008</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3518,10 +3515,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112778343</v>
+        <v>112778458</v>
       </c>
       <c r="B27" t="n">
-        <v>91306</v>
+        <v>91292</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3534,21 +3531,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>3100</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3561,10 +3558,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>801628</v>
+        <v>801334</v>
       </c>
       <c r="R27" t="n">
-        <v>7225850</v>
+        <v>7225995</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3634,10 +3631,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112779914</v>
+        <v>112778326</v>
       </c>
       <c r="B28" t="n">
-        <v>91290</v>
+        <v>91298</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3646,25 +3643,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3677,10 +3674,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>801630</v>
+        <v>801667</v>
       </c>
       <c r="R28" t="n">
-        <v>7225910</v>
+        <v>7225861</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3753,7 +3750,7 @@
         <v>111959726</v>
       </c>
       <c r="B29" t="n">
-        <v>90924</v>
+        <v>90940</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3863,10 +3860,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112779921</v>
+        <v>112387433</v>
       </c>
       <c r="B30" t="n">
-        <v>91290</v>
+        <v>91306</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3906,13 +3903,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>801657</v>
+        <v>801200</v>
       </c>
       <c r="R30" t="n">
-        <v>7225926</v>
+        <v>7225979</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3979,10 +3976,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112387433</v>
+        <v>112778562</v>
       </c>
       <c r="B31" t="n">
-        <v>91290</v>
+        <v>91306</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4022,13 +4019,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>801200</v>
+        <v>801193</v>
       </c>
       <c r="R31" t="n">
-        <v>7225979</v>
+        <v>7226012</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4095,10 +4092,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111959727</v>
+        <v>112778442</v>
       </c>
       <c r="B32" t="n">
-        <v>91333</v>
+        <v>90065</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4111,38 +4108,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Degernäsmyren, Vb</t>
+          <t>degernäsgrundet, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>801306</v>
+        <v>801472</v>
       </c>
       <c r="R32" t="n">
-        <v>7226050</v>
+        <v>7225939</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4171,7 +4170,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4181,7 +4180,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4190,6 +4189,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112779893</v>
+        <v>111959727</v>
       </c>
       <c r="B33" t="n">
-        <v>91290</v>
+        <v>91349</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4220,44 +4220,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>degernäsgrundet, Vb</t>
+          <t>Degernäsmyren, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>801160</v>
+        <v>801306</v>
       </c>
       <c r="R33" t="n">
-        <v>7225992</v>
+        <v>7226050</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4286,7 +4284,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4296,7 +4294,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4305,7 +4303,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4324,10 +4321,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111959803</v>
+        <v>112780264</v>
       </c>
       <c r="B34" t="n">
-        <v>91276</v>
+        <v>91306</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4336,42 +4333,44 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Degernäsmyren, Vb</t>
+          <t>degernäsgrundet, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>801306</v>
+        <v>801228</v>
       </c>
       <c r="R34" t="n">
-        <v>7226050</v>
+        <v>7226025</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4400,7 +4399,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4410,7 +4409,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4419,6 +4418,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112778481</v>
+        <v>112778337</v>
       </c>
       <c r="B35" t="n">
-        <v>91276</v>
+        <v>91322</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4453,21 +4453,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>801343</v>
+        <v>801319</v>
       </c>
       <c r="R35" t="n">
-        <v>7225967</v>
+        <v>7226001</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112778368</v>
+        <v>112778533</v>
       </c>
       <c r="B36" t="n">
-        <v>90924</v>
+        <v>91306</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4565,25 +4565,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4599,7 +4599,7 @@
         <v>801302</v>
       </c>
       <c r="R36" t="n">
-        <v>7226025</v>
+        <v>7225991</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112778526</v>
+        <v>112778343</v>
       </c>
       <c r="B37" t="n">
-        <v>91302</v>
+        <v>91322</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>801294</v>
+        <v>801628</v>
       </c>
       <c r="R37" t="n">
-        <v>7226013</v>
+        <v>7225850</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4785,10 +4785,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112778562</v>
+        <v>112778368</v>
       </c>
       <c r="B38" t="n">
-        <v>91290</v>
+        <v>90940</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4797,25 +4797,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>801193</v>
+        <v>801302</v>
       </c>
       <c r="R38" t="n">
-        <v>7226012</v>
+        <v>7226025</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112778458</v>
+        <v>112778412</v>
       </c>
       <c r="B39" t="n">
-        <v>91276</v>
+        <v>91349</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4917,21 +4917,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3100</v>
+        <v>5448</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>801334</v>
+        <v>801332</v>
       </c>
       <c r="R39" t="n">
-        <v>7225995</v>
+        <v>7225981</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5017,10 +5017,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112778514</v>
+        <v>112780261</v>
       </c>
       <c r="B40" t="n">
-        <v>91290</v>
+        <v>91306</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>801257</v>
+        <v>801272</v>
       </c>
       <c r="R40" t="n">
-        <v>7226008</v>
+        <v>7226055</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5133,10 +5133,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112778391</v>
+        <v>112778350</v>
       </c>
       <c r="B41" t="n">
-        <v>91333</v>
+        <v>90063</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5149,21 +5149,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5448</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5176,13 +5176,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>801314</v>
+        <v>801521</v>
       </c>
       <c r="R41" t="n">
-        <v>7226071</v>
+        <v>7225910</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112778337</v>
+        <v>112779893</v>
       </c>
       <c r="B42" t="n">
         <v>91306</v>
@@ -5261,25 +5261,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5292,10 +5292,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>801319</v>
+        <v>801160</v>
       </c>
       <c r="R42" t="n">
-        <v>7226001</v>
+        <v>7225992</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5365,10 +5365,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112778523</v>
+        <v>112387446</v>
       </c>
       <c r="B43" t="n">
-        <v>91302</v>
+        <v>91306</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5381,21 +5381,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5408,13 +5408,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>801260</v>
+        <v>801284</v>
       </c>
       <c r="R43" t="n">
-        <v>7225988</v>
+        <v>7225974</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112778466</v>
+        <v>112778523</v>
       </c>
       <c r="B44" t="n">
-        <v>91276</v>
+        <v>91318</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5493,25 +5493,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>801318</v>
+        <v>801260</v>
       </c>
       <c r="R44" t="n">
-        <v>7226056</v>
+        <v>7225988</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>

--- a/artfynd/A 29807-2021 artfynd.xlsx
+++ b/artfynd/A 29807-2021 artfynd.xlsx
@@ -2587,10 +2587,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112778397</v>
+        <v>112779902</v>
       </c>
       <c r="B19" t="n">
-        <v>91292</v>
+        <v>91318</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,25 +2599,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801307</v>
+        <v>801318</v>
       </c>
       <c r="R19" t="n">
-        <v>7226037</v>
+        <v>7225959</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112778466</v>
+        <v>112778397</v>
       </c>
       <c r="B20" t="n">
         <v>91292</v>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>801318</v>
+        <v>801307</v>
       </c>
       <c r="R20" t="n">
-        <v>7226056</v>
+        <v>7226037</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112778481</v>
+        <v>112778466</v>
       </c>
       <c r="B21" t="n">
         <v>91292</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>801343</v>
+        <v>801318</v>
       </c>
       <c r="R21" t="n">
-        <v>7225967</v>
+        <v>7226056</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2935,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112779902</v>
+        <v>112778481</v>
       </c>
       <c r="B22" t="n">
-        <v>91318</v>
+        <v>91292</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2947,25 +2947,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2978,10 +2978,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>801318</v>
+        <v>801343</v>
       </c>
       <c r="R22" t="n">
-        <v>7225959</v>
+        <v>7225967</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3976,10 +3976,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112778562</v>
+        <v>112778442</v>
       </c>
       <c r="B31" t="n">
-        <v>91306</v>
+        <v>90065</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3988,25 +3988,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>801193</v>
+        <v>801472</v>
       </c>
       <c r="R31" t="n">
-        <v>7226012</v>
+        <v>7225939</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4092,10 +4092,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112778442</v>
+        <v>111959727</v>
       </c>
       <c r="B32" t="n">
-        <v>90065</v>
+        <v>91349</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4108,40 +4108,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>5448</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>degernäsgrundet, Vb</t>
+          <t>Degernäsmyren, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>801472</v>
+        <v>801306</v>
       </c>
       <c r="R32" t="n">
-        <v>7225939</v>
+        <v>7226050</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4170,7 +4168,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4180,7 +4178,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4189,7 +4187,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4208,10 +4205,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111959727</v>
+        <v>112780264</v>
       </c>
       <c r="B33" t="n">
-        <v>91349</v>
+        <v>91306</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4220,42 +4217,44 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Degernäsmyren, Vb</t>
+          <t>degernäsgrundet, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>801306</v>
+        <v>801228</v>
       </c>
       <c r="R33" t="n">
-        <v>7226050</v>
+        <v>7226025</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4284,7 +4283,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4294,7 +4293,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4303,6 +4302,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4321,7 +4321,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112780264</v>
+        <v>112778562</v>
       </c>
       <c r="B34" t="n">
         <v>91306</v>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>801228</v>
+        <v>801193</v>
       </c>
       <c r="R34" t="n">
-        <v>7226025</v>
+        <v>7226012</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>

--- a/artfynd/A 29807-2021 artfynd.xlsx
+++ b/artfynd/A 29807-2021 artfynd.xlsx
@@ -2242,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112387439</v>
+        <v>112778466</v>
       </c>
       <c r="B16" t="n">
-        <v>91306</v>
+        <v>91292</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,25 +2254,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801241</v>
+        <v>801318</v>
       </c>
       <c r="R16" t="n">
-        <v>7225973</v>
+        <v>7226056</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112779921</v>
+        <v>112778533</v>
       </c>
       <c r="B17" t="n">
         <v>91306</v>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801657</v>
+        <v>801302</v>
       </c>
       <c r="R17" t="n">
-        <v>7225926</v>
+        <v>7225991</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2474,10 +2474,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111959803</v>
+        <v>112778514</v>
       </c>
       <c r="B18" t="n">
-        <v>91292</v>
+        <v>91306</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2486,42 +2486,44 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Degernäsmyren, Vb</t>
+          <t>degernäsgrundet, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801306</v>
+        <v>801257</v>
       </c>
       <c r="R18" t="n">
-        <v>7226050</v>
+        <v>7226008</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2550,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2560,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2569,6 +2571,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2587,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112779902</v>
+        <v>112387446</v>
       </c>
       <c r="B19" t="n">
-        <v>91318</v>
+        <v>91306</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,21 +2606,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2630,13 +2633,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801318</v>
+        <v>801284</v>
       </c>
       <c r="R19" t="n">
-        <v>7225959</v>
+        <v>7225974</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2703,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112778397</v>
+        <v>112780264</v>
       </c>
       <c r="B20" t="n">
-        <v>91292</v>
+        <v>91306</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2715,25 +2718,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2746,13 +2749,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>801307</v>
+        <v>801228</v>
       </c>
       <c r="R20" t="n">
-        <v>7226037</v>
+        <v>7226025</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2819,10 +2822,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112778466</v>
+        <v>112778343</v>
       </c>
       <c r="B21" t="n">
-        <v>91292</v>
+        <v>91322</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2835,21 +2838,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2862,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>801318</v>
+        <v>801628</v>
       </c>
       <c r="R21" t="n">
-        <v>7226056</v>
+        <v>7225850</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2935,10 +2938,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112778481</v>
+        <v>112778337</v>
       </c>
       <c r="B22" t="n">
-        <v>91292</v>
+        <v>91322</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2951,21 +2954,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2978,10 +2981,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>801343</v>
+        <v>801319</v>
       </c>
       <c r="R22" t="n">
-        <v>7225967</v>
+        <v>7226001</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3051,7 +3054,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112779914</v>
+        <v>112780261</v>
       </c>
       <c r="B23" t="n">
         <v>91306</v>
@@ -3094,10 +3097,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>801630</v>
+        <v>801272</v>
       </c>
       <c r="R23" t="n">
-        <v>7225910</v>
+        <v>7226055</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3167,10 +3170,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112778391</v>
+        <v>112778442</v>
       </c>
       <c r="B24" t="n">
-        <v>91349</v>
+        <v>90065</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3183,21 +3186,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3210,13 +3213,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>801314</v>
+        <v>801472</v>
       </c>
       <c r="R24" t="n">
-        <v>7226071</v>
+        <v>7225939</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3283,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112778526</v>
+        <v>112778562</v>
       </c>
       <c r="B25" t="n">
-        <v>91318</v>
+        <v>91306</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3299,21 +3302,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3326,10 +3329,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>801294</v>
+        <v>801193</v>
       </c>
       <c r="R25" t="n">
-        <v>7226013</v>
+        <v>7226012</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3399,10 +3402,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112778514</v>
+        <v>112778391</v>
       </c>
       <c r="B26" t="n">
-        <v>91306</v>
+        <v>91349</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3411,25 +3414,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3442,13 +3445,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>801257</v>
+        <v>801314</v>
       </c>
       <c r="R26" t="n">
-        <v>7226008</v>
+        <v>7226071</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3515,10 +3518,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112778458</v>
+        <v>112387433</v>
       </c>
       <c r="B27" t="n">
-        <v>91292</v>
+        <v>91306</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3527,25 +3530,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3558,13 +3561,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>801334</v>
+        <v>801200</v>
       </c>
       <c r="R27" t="n">
-        <v>7225995</v>
+        <v>7225979</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3631,10 +3634,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112778326</v>
+        <v>112779914</v>
       </c>
       <c r="B28" t="n">
-        <v>91298</v>
+        <v>91306</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3643,25 +3646,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3674,10 +3677,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>801667</v>
+        <v>801630</v>
       </c>
       <c r="R28" t="n">
-        <v>7225861</v>
+        <v>7225910</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3747,10 +3750,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111959726</v>
+        <v>112778523</v>
       </c>
       <c r="B29" t="n">
-        <v>90940</v>
+        <v>91318</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3759,42 +3762,44 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Degernäsmyren, Vb</t>
+          <t>degernäsgrundet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>801306</v>
+        <v>801260</v>
       </c>
       <c r="R29" t="n">
-        <v>7226050</v>
+        <v>7225988</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3823,7 +3828,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3833,7 +3838,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3842,6 +3847,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3860,10 +3866,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112387433</v>
+        <v>112778326</v>
       </c>
       <c r="B30" t="n">
-        <v>91306</v>
+        <v>91298</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3872,25 +3878,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3903,13 +3909,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>801200</v>
+        <v>801667</v>
       </c>
       <c r="R30" t="n">
-        <v>7225979</v>
+        <v>7225861</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3976,10 +3982,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112778442</v>
+        <v>111959727</v>
       </c>
       <c r="B31" t="n">
-        <v>90065</v>
+        <v>91349</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3992,40 +3998,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>5448</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>degernäsgrundet, Vb</t>
+          <t>Degernäsmyren, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>801472</v>
+        <v>801306</v>
       </c>
       <c r="R31" t="n">
-        <v>7225939</v>
+        <v>7226050</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4054,7 +4058,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4064,7 +4068,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4073,7 +4077,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4092,10 +4095,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111959727</v>
+        <v>111959803</v>
       </c>
       <c r="B32" t="n">
-        <v>91349</v>
+        <v>91292</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4108,21 +4111,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5448</v>
+        <v>3100</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4205,10 +4208,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112780264</v>
+        <v>112778412</v>
       </c>
       <c r="B33" t="n">
-        <v>91306</v>
+        <v>91349</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4217,25 +4220,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4248,10 +4251,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>801228</v>
+        <v>801332</v>
       </c>
       <c r="R33" t="n">
-        <v>7226025</v>
+        <v>7225981</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4321,10 +4324,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112778562</v>
+        <v>111959726</v>
       </c>
       <c r="B34" t="n">
-        <v>91306</v>
+        <v>90940</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4333,44 +4336,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>degernäsgrundet, Vb</t>
+          <t>Degernäsmyren, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>801193</v>
+        <v>801306</v>
       </c>
       <c r="R34" t="n">
-        <v>7226012</v>
+        <v>7226050</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4399,7 +4400,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4409,7 +4410,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4418,7 +4419,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112778337</v>
+        <v>112387439</v>
       </c>
       <c r="B35" t="n">
-        <v>91322</v>
+        <v>91306</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4449,25 +4449,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4480,13 +4480,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>801319</v>
+        <v>801241</v>
       </c>
       <c r="R35" t="n">
-        <v>7226001</v>
+        <v>7225973</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112778533</v>
+        <v>112778397</v>
       </c>
       <c r="B36" t="n">
-        <v>91306</v>
+        <v>91292</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4565,25 +4565,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4596,13 +4596,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>801302</v>
+        <v>801307</v>
       </c>
       <c r="R36" t="n">
-        <v>7225991</v>
+        <v>7226037</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112778343</v>
+        <v>112779893</v>
       </c>
       <c r="B37" t="n">
-        <v>91322</v>
+        <v>91306</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>801628</v>
+        <v>801160</v>
       </c>
       <c r="R37" t="n">
-        <v>7225850</v>
+        <v>7225992</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4785,10 +4785,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112778368</v>
+        <v>112778350</v>
       </c>
       <c r="B38" t="n">
-        <v>90940</v>
+        <v>90063</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4801,21 +4801,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4745</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>801302</v>
+        <v>801521</v>
       </c>
       <c r="R38" t="n">
-        <v>7226025</v>
+        <v>7225910</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112778412</v>
+        <v>112779902</v>
       </c>
       <c r="B39" t="n">
-        <v>91349</v>
+        <v>91318</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4913,25 +4913,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5448</v>
+        <v>4366</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>801332</v>
+        <v>801318</v>
       </c>
       <c r="R39" t="n">
-        <v>7225981</v>
+        <v>7225959</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5017,10 +5017,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112780261</v>
+        <v>112778526</v>
       </c>
       <c r="B40" t="n">
-        <v>91306</v>
+        <v>91318</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5033,21 +5033,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>801272</v>
+        <v>801294</v>
       </c>
       <c r="R40" t="n">
-        <v>7226055</v>
+        <v>7226013</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5133,10 +5133,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112778350</v>
+        <v>112778481</v>
       </c>
       <c r="B41" t="n">
-        <v>90063</v>
+        <v>91292</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5149,21 +5149,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>3100</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>801521</v>
+        <v>801343</v>
       </c>
       <c r="R41" t="n">
-        <v>7225910</v>
+        <v>7225967</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5249,10 +5249,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112779893</v>
+        <v>112778368</v>
       </c>
       <c r="B42" t="n">
-        <v>91306</v>
+        <v>90940</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5261,25 +5261,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5292,10 +5292,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>801160</v>
+        <v>801302</v>
       </c>
       <c r="R42" t="n">
-        <v>7225992</v>
+        <v>7226025</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5365,10 +5365,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112387446</v>
+        <v>112778458</v>
       </c>
       <c r="B43" t="n">
-        <v>91306</v>
+        <v>91292</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5377,25 +5377,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5408,13 +5408,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>801284</v>
+        <v>801334</v>
       </c>
       <c r="R43" t="n">
-        <v>7225974</v>
+        <v>7225995</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112778523</v>
+        <v>112779921</v>
       </c>
       <c r="B44" t="n">
-        <v>91318</v>
+        <v>91306</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5497,21 +5497,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>801260</v>
+        <v>801657</v>
       </c>
       <c r="R44" t="n">
-        <v>7225988</v>
+        <v>7225926</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>

--- a/artfynd/A 29807-2021 artfynd.xlsx
+++ b/artfynd/A 29807-2021 artfynd.xlsx
@@ -2242,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112778466</v>
+        <v>111959726</v>
       </c>
       <c r="B16" t="n">
-        <v>91292</v>
+        <v>90952</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2258,40 +2258,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3100</v>
+        <v>4745</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>degernäsgrundet, Vb</t>
+          <t>Degernäsmyren, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801318</v>
+        <v>801306</v>
       </c>
       <c r="R16" t="n">
-        <v>7226056</v>
+        <v>7226050</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2320,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2330,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,7 +2337,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2358,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112778533</v>
+        <v>112387433</v>
       </c>
       <c r="B17" t="n">
-        <v>91306</v>
+        <v>91318</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,13 +2398,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801302</v>
+        <v>801200</v>
       </c>
       <c r="R17" t="n">
-        <v>7225991</v>
+        <v>7225979</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2474,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112778514</v>
+        <v>112778481</v>
       </c>
       <c r="B18" t="n">
-        <v>91306</v>
+        <v>91304</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2486,25 +2483,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2517,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801257</v>
+        <v>801343</v>
       </c>
       <c r="R18" t="n">
-        <v>7226008</v>
+        <v>7225967</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2590,10 +2587,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112387446</v>
+        <v>111959803</v>
       </c>
       <c r="B19" t="n">
-        <v>91306</v>
+        <v>91304</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2602,41 +2599,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>degernäsgrundet, Vb</t>
+          <t>Degernäsmyren, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801284</v>
+        <v>801306</v>
       </c>
       <c r="R19" t="n">
-        <v>7225974</v>
+        <v>7226050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2668,7 +2663,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2678,7 +2673,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2687,7 +2682,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2706,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112780264</v>
+        <v>111959727</v>
       </c>
       <c r="B20" t="n">
-        <v>91306</v>
+        <v>91361</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,44 +2712,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>degernäsgrundet, Vb</t>
+          <t>Degernäsmyren, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>801228</v>
+        <v>801306</v>
       </c>
       <c r="R20" t="n">
-        <v>7226025</v>
+        <v>7226050</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2784,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2794,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,7 +2795,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2822,10 +2813,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112778343</v>
+        <v>112779914</v>
       </c>
       <c r="B21" t="n">
-        <v>91322</v>
+        <v>91318</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,25 +2825,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2865,10 +2856,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>801628</v>
+        <v>801630</v>
       </c>
       <c r="R21" t="n">
-        <v>7225850</v>
+        <v>7225910</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2938,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112778337</v>
+        <v>112780261</v>
       </c>
       <c r="B22" t="n">
-        <v>91322</v>
+        <v>91318</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2950,25 +2941,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2981,10 +2972,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>801319</v>
+        <v>801272</v>
       </c>
       <c r="R22" t="n">
-        <v>7226001</v>
+        <v>7226055</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3054,10 +3045,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112780261</v>
+        <v>112778466</v>
       </c>
       <c r="B23" t="n">
-        <v>91306</v>
+        <v>91304</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3066,25 +3057,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3097,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>801272</v>
+        <v>801318</v>
       </c>
       <c r="R23" t="n">
-        <v>7226055</v>
+        <v>7226056</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3170,10 +3161,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112778442</v>
+        <v>112778533</v>
       </c>
       <c r="B24" t="n">
-        <v>90065</v>
+        <v>91318</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3182,25 +3173,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3213,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>801472</v>
+        <v>801302</v>
       </c>
       <c r="R24" t="n">
-        <v>7225939</v>
+        <v>7225991</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3286,10 +3277,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112778562</v>
+        <v>112778514</v>
       </c>
       <c r="B25" t="n">
-        <v>91306</v>
+        <v>91318</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3329,10 +3320,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>801193</v>
+        <v>801257</v>
       </c>
       <c r="R25" t="n">
-        <v>7226012</v>
+        <v>7226008</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3405,7 +3396,7 @@
         <v>112778391</v>
       </c>
       <c r="B26" t="n">
-        <v>91349</v>
+        <v>91361</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3518,10 +3509,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112387433</v>
+        <v>112778397</v>
       </c>
       <c r="B27" t="n">
-        <v>91306</v>
+        <v>91304</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3530,25 +3521,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3561,13 +3552,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>801200</v>
+        <v>801307</v>
       </c>
       <c r="R27" t="n">
-        <v>7225979</v>
+        <v>7226037</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3634,10 +3625,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112779914</v>
+        <v>112778368</v>
       </c>
       <c r="B28" t="n">
-        <v>91306</v>
+        <v>90952</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3646,25 +3637,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3677,10 +3668,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>801630</v>
+        <v>801302</v>
       </c>
       <c r="R28" t="n">
-        <v>7225910</v>
+        <v>7226025</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3750,7 +3741,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112778523</v>
+        <v>112387439</v>
       </c>
       <c r="B29" t="n">
         <v>91318</v>
@@ -3766,21 +3757,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3793,13 +3784,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>801260</v>
+        <v>801241</v>
       </c>
       <c r="R29" t="n">
-        <v>7225988</v>
+        <v>7225973</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3866,10 +3857,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112778326</v>
+        <v>112778412</v>
       </c>
       <c r="B30" t="n">
-        <v>91298</v>
+        <v>91361</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3882,21 +3873,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3909,10 +3900,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>801667</v>
+        <v>801332</v>
       </c>
       <c r="R30" t="n">
-        <v>7225861</v>
+        <v>7225981</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3982,10 +3973,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111959727</v>
+        <v>112779902</v>
       </c>
       <c r="B31" t="n">
-        <v>91349</v>
+        <v>91330</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3994,42 +3985,44 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5448</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Degernäsmyren, Vb</t>
+          <t>degernäsgrundet, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>801306</v>
+        <v>801318</v>
       </c>
       <c r="R31" t="n">
-        <v>7226050</v>
+        <v>7225959</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4058,7 +4051,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4068,7 +4061,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4077,6 +4070,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4095,10 +4089,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111959803</v>
+        <v>112778458</v>
       </c>
       <c r="B32" t="n">
-        <v>91292</v>
+        <v>91304</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4129,20 +4123,22 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Degernäsmyren, Vb</t>
+          <t>degernäsgrundet, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>801306</v>
+        <v>801334</v>
       </c>
       <c r="R32" t="n">
-        <v>7226050</v>
+        <v>7225995</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4171,7 +4167,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4181,7 +4177,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4190,6 +4186,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4208,10 +4205,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112778412</v>
+        <v>112387446</v>
       </c>
       <c r="B33" t="n">
-        <v>91349</v>
+        <v>91318</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4220,25 +4217,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4251,13 +4248,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>801332</v>
+        <v>801284</v>
       </c>
       <c r="R33" t="n">
-        <v>7225981</v>
+        <v>7225974</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4324,10 +4321,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111959726</v>
+        <v>112778523</v>
       </c>
       <c r="B34" t="n">
-        <v>90940</v>
+        <v>91330</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4336,42 +4333,44 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Degernäsmyren, Vb</t>
+          <t>degernäsgrundet, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>801306</v>
+        <v>801260</v>
       </c>
       <c r="R34" t="n">
-        <v>7226050</v>
+        <v>7225988</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4400,7 +4399,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4410,7 +4409,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4419,6 +4418,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112387439</v>
+        <v>112778526</v>
       </c>
       <c r="B35" t="n">
-        <v>91306</v>
+        <v>91330</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4453,21 +4453,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4480,13 +4480,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>801241</v>
+        <v>801294</v>
       </c>
       <c r="R35" t="n">
-        <v>7225973</v>
+        <v>7226013</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112778397</v>
+        <v>112778326</v>
       </c>
       <c r="B36" t="n">
-        <v>91292</v>
+        <v>91310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4596,13 +4596,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>801307</v>
+        <v>801667</v>
       </c>
       <c r="R36" t="n">
-        <v>7226037</v>
+        <v>7225861</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112779893</v>
+        <v>112778343</v>
       </c>
       <c r="B37" t="n">
-        <v>91306</v>
+        <v>91334</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>801160</v>
+        <v>801628</v>
       </c>
       <c r="R37" t="n">
-        <v>7225992</v>
+        <v>7225850</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4785,10 +4785,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112778350</v>
+        <v>112780264</v>
       </c>
       <c r="B38" t="n">
-        <v>90063</v>
+        <v>91318</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4797,25 +4797,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>801521</v>
+        <v>801228</v>
       </c>
       <c r="R38" t="n">
-        <v>7225910</v>
+        <v>7226025</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4901,7 +4901,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112779902</v>
+        <v>112779921</v>
       </c>
       <c r="B39" t="n">
         <v>91318</v>
@@ -4917,21 +4917,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>801318</v>
+        <v>801657</v>
       </c>
       <c r="R39" t="n">
-        <v>7225959</v>
+        <v>7225926</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5017,7 +5017,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112778526</v>
+        <v>112778562</v>
       </c>
       <c r="B40" t="n">
         <v>91318</v>
@@ -5033,21 +5033,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>801294</v>
+        <v>801193</v>
       </c>
       <c r="R40" t="n">
-        <v>7226013</v>
+        <v>7226012</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5133,10 +5133,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112778481</v>
+        <v>112779893</v>
       </c>
       <c r="B41" t="n">
-        <v>91292</v>
+        <v>91318</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5145,25 +5145,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>801343</v>
+        <v>801160</v>
       </c>
       <c r="R41" t="n">
-        <v>7225967</v>
+        <v>7225992</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5249,10 +5249,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112778368</v>
+        <v>112778350</v>
       </c>
       <c r="B42" t="n">
-        <v>90940</v>
+        <v>90075</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4745</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5292,10 +5292,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>801302</v>
+        <v>801521</v>
       </c>
       <c r="R42" t="n">
-        <v>7226025</v>
+        <v>7225910</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5365,10 +5365,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112778458</v>
+        <v>112778442</v>
       </c>
       <c r="B43" t="n">
-        <v>91292</v>
+        <v>90077</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5381,21 +5381,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3100</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>801334</v>
+        <v>801472</v>
       </c>
       <c r="R43" t="n">
-        <v>7225995</v>
+        <v>7225939</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112779921</v>
+        <v>112778337</v>
       </c>
       <c r="B44" t="n">
-        <v>91306</v>
+        <v>91334</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5493,25 +5493,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>801657</v>
+        <v>801319</v>
       </c>
       <c r="R44" t="n">
-        <v>7225926</v>
+        <v>7226001</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>

--- a/artfynd/A 29807-2021 artfynd.xlsx
+++ b/artfynd/A 29807-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
